--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_694_Sierra_Leone.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_694_Sierra_Leone.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb5548083d4ff4b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra9d89623c8b44d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4aaec936241c4afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd41ac8ae7b8e44aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9601a9f53c5a4df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R976262c299e54ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R643ff8c99825419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd657307117b44260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra0ebb445a3cd43b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0c095fce75fd4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf53861a9bf024ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R62a00f91bbb44f82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ694CommercialTable" displayName="EEZ694CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ694CommercialTable" displayName="EEZ694CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ694FunctionalTable" displayName="EEZ694FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ694FunctionalTable" displayName="EEZ694FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ694ValidationTable" displayName="EEZ694ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ694ValidationTable" displayName="EEZ694ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -15032,7 +14986,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5343f1d29eb64b33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72575abdc9c0438d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15042,20 +14996,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -15063,660 +15007,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>119.4452833038</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>119.4452833038</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$215,A2,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>15387.53326679797</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>15387.53326679797</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>95.2923884459</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.410069054933802</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2570.804520688255</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>95.2923884459</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2804.1624024677285</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$215,A3,'Species'!$U$2:$U$215))</x:f>
-        <x:v>267215.332921343</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.410069054933802</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2570.804520688255</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>244978.10300390093</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>22237.229917442048</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0907723165653216</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.09077231656532156</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>23402.903350477703</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3059750203536513</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>202.2902822490331</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>23402.903350477703</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>203.08204761496066</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$215,A4,'Species'!$U$2:$U$215))</x:f>
-        <x:v>4752709.532550035</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3059750203536513</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>202.2902822490331</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4734179.924214978</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>18529.608335057274</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0039140059380252</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.003914005938025234</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>252.07081954699999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.176778197854014</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>150.23744799592774</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>252.07081954699999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>156.0529847638321</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$215,A5,'Species'!$U$2:$U$215))</x:f>
-        <x:v>39336.403762174654</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.176778197854014</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>150.23744799592774</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>37870.476642983296</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1465.9271191913576</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0387089693380707</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.03870896933807056</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>179841.5314351926</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.617460603690516</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>41.44389871817527</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>179841.5314351926</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>55.79478632442218</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$215,A6,'Species'!$U$2:$U$215))</x:f>
-        <x:v>10034219.818683425</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.617460603690516</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>41.44389871817527</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7453334.214121656</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2580885.6045617694</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3462726251657717</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.3462726251657717</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6893.6491129279</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.019289035535604</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.454157421550716</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6893.6491129279</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.499862001865294</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$215,A7,'Species'!$U$2:$U$215))</x:f>
-        <x:v>72382.36437502404</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.019289035535604</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.454157421550716</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>72067.29303548172</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>315.0713395423227</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0043719047333608</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.004371904733360805</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>69916.83588096312</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3002941423325627</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>199.66141394285964</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>69916.83588096312</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>205.68102919308396</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$215,A8,'Species'!$U$2:$U$215))</x:f>
-        <x:v>14380566.761920435</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3002941423325627</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>199.66141394285964</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>13959694.310403958</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>420872.4515164774</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0301491166037073</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.030149116603707234</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>147327.97703339998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.7675415980704083</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>585.519816536043</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>147327.97703339998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>829.0715122016389</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$215,A9,'Species'!$U$2:$U$215))</x:f>
-        <x:v>122145428.70868926</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.7675415980704083</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>585.519816536043</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>86263450.0832227</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>35881978.625466555</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4159580748375982</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.41595807483759806</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>26.0098614115</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9114241083812016</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>815.5002685286728</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>26.0098614115</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>822.0366398622443</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$215,A10,'Species'!$U$2:$U$215))</x:f>
-        <x:v>21381.05907799211</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9114241083812016</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>815.5002685286728</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>21211.048965471815</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>170.0101125202964</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0080151676042541</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.008015167604254065</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5624.0430896889</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.216917145166622</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1647.847984595331</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5624.0430896889</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2333.214207385464</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$215,A11,'Species'!$U$2:$U$215))</x:f>
-        <x:v>13122097.239810184</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.216917145166622</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1647.847984595331</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>9267568.070621151</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>3854529.169189032</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4159159274381985</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4159159274381985</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>9017.248511974</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.425195993266395</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2661.9260925208314</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>9017.248511974</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2668.5301011628408</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$215,A12,'Species'!$U$2:$U$215))</x:f>
-        <x:v>24062799.08386845</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.425195993266395</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2661.9260925208314</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>24003249.09676823</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>59549.98710022122</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0024809135988277</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0024809135988277087</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7c05f93e9984959"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R525f17d639384360"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15726,20 +15241,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -15747,1362 +15252,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3385.6079216567</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.664803732358886</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>462.17210801644296</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3385.6079216567</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>468.054451602418</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$215,A2,'Species'!$U$2:$U$215))</x:f>
-        <x:v>1584648.859111829</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.664803732358886</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>462.17210801644296</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1564733.5500692453</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>19915.309042583685</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.012727604033097</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.01272760403309711</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.5049341954</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.5049341954</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$215,A3,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1104.6756553159641</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1104.6756553159641</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1013.9420786594001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.418467863246534</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2621.0050833486484</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1013.9420786594001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2625.3261809163773</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$215,A4,'Species'!$U$2:$U$215))</x:f>
-        <x:v>2661928.685037296</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.418467863246534</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2621.0050833486484</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2657547.342387383</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4381.342649912927</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0016486414296488</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0016486414296488089</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>25329.3906613288</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.873185532934276</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>746.7677134519387</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>25329.3906613288</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>765.8289497774559</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$215,A5,'Species'!$U$2:$U$215))</x:f>
-        <x:v>19397980.648668338</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.873185532934276</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>746.7677134519387</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>18915171.1472914</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>482809.5013769381</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.025524987197701</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.025524987197701094</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>18482.3017844843</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.399338678728255</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2508.064370965827</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>18482.3017844843</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2534.0069851300323</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$215,A6,'Species'!$U$2:$U$215))</x:f>
-        <x:v>46834281.82316448</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.399338678728255</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2508.064370965827</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>46354802.599103205</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>479479.22406127304</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.010343679558039</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.010343679558038917</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1538.9433556070999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7198130965359875</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.5816521111215</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1538.9433556070999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>528.5591679298441</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$215,A7,'Species'!$U$2:$U$215))</x:f>
-        <x:v>813422.6195308509</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7198130965359875</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.5816521111215</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>807301.4479898055</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>6121.17154104542</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0075822625566784</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.007582262556678478</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>572.3046836313999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4197479102856643</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>262.87416747735</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>572.3046836313999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>281.92155036558637</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$215,A8,'Species'!$U$2:$U$215))</x:f>
-        <x:v>161345.0236908507</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4197479102856643</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>262.87416747735</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>150444.11725299244</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>10900.90643785827</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0724581767429755</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0724581767429756</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4081.2105349635</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.404665959105815</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2539.0190485549783</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4081.2105349635</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3015.1642416560844</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$215,A9,'Species'!$U$2:$U$215))</x:f>
-        <x:v>12305520.067692043</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.404665959105815</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2539.0190485549783</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10362271.28943558</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1943248.778256463</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1875311622305835</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.18753116223058364</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>166.58167022970002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.127316142826846</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>134.06522544276413</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>166.58167022970002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>136.13866675375897</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$215,A10,'Species'!$U$2:$U$215))</x:f>
-        <x:v>22678.2064906857</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.127316142826846</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>134.06522544276413</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>22332.809173976922</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>345.3973167087788</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0154659144766818</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.015465914476681667</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>96.8388587035</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.480086963966499</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3020.5565019210253</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>96.8388587035</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3075.3248759677094</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$215,A11,'Species'!$U$2:$U$215))</x:f>
-        <x:v>297810.95113119564</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.480086963966499</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3020.5565019210253</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>292507.2442954684</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>5303.706835727266</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0181318819932195</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.018131881993219516</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>78.00319293000001</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.080864618251596</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1204.6603554765165</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>78.00319293000001</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1205.1940408582468</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$215,A12,'Species'!$U$2:$U$215))</x:f>
-        <x:v>94008.98328715214</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.080864618251596</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1204.6603554765165</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>93967.35412335712</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>41.62916379501985</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0004430173030132</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0004430173030132413</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>12916.3708348995</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.377917953339383</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>238.73602216045734</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>12916.3708348995</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>247.09769941903622</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$215,A13,'Species'!$U$2:$U$215))</x:f>
-        <x:v>3191605.5181468027</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.377917953339383</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>238.73602216045734</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>3083602.993873252</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>108002.5242735506</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.035024782531389</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.03502478253138897</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>98826.69312835591</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4463246674207255</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>279.4632255946387</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>98826.69312835591</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>374.4094761280087</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$215,A14,'Species'!$U$2:$U$215))</x:f>
-        <x:v>37001650.40165121</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4463246674207255</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>279.4632255946387</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>27618426.436501857</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>9383223.965149354</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3397450606652965</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.3397450606652966</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>180499.54784213004</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.8551460072405814</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>71.6384213875158</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>180499.54784213004</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>209.14104595992228</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$215,A15,'Species'!$U$2:$U$215))</x:f>
-        <x:v>37749864.23099611</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.8551460072405814</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>71.6384213875158</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>12930702.66857058</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>24819161.56242553</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.9193977464775434</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.9193977464775436</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>11658.0091097944</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.881036145067028</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>760.389559318949</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>11658.0091097944</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1445.321082164224</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$215,A16,'Species'!$U$2:$U$215))</x:f>
-        <x:v>16849566.342448425</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.881036145067028</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>760.389559318949</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>8864628.409532856</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>7984937.932915568</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.9007639761107995</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.9007639761107995</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>6893.6537018931</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.019289308937548</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>10.454164002771485</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>6893.6537018931</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>10.499872929320807</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$215,A17,'Species'!$U$2:$U$215))</x:f>
-        <x:v>72382.48788861954</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.019289308937548</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>10.454164002771485</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>72067.38637790324</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>315.1015107162966</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0043723177230819</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.004372317723081888</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>23236.321680248</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.307255829538054</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>202.88775169969932</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>23236.321680248</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>203.56196609552475</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$215,A18,'Species'!$U$2:$U$215))</x:f>
-        <x:v>4730031.32605935</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.307255829538054</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>202.88775169969932</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>4714365.063476496</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>15666.262582853436</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0033230906753965</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0033230906753964284</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1072.2949915336</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1072.2949915336</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$215,A19,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>114898.47843378477</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>114898.47843378477</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>10077.857522311398</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.2613304605087587</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>182.52840572170103</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>10077.857522311398</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>244.52120222678505</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$215,A20,'Species'!$U$2:$U$215))</x:f>
-        <x:v>2464249.8372258325</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.2613304605087587</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>182.52840572170103</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1839495.2666379516</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>624754.5705878809</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.3396336929584742</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.33963369295847434</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>42334.4752285137</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.772835836283325</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>59.27012406124116</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>42334.4752285137</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>59.57201637695576</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$215,A21,'Species'!$U$2:$U$215))</x:f>
-        <x:v>2521950.051622846</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.772835836283325</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>59.27012406124116</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2509169.5988615477</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>12780.452761298511</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0050934989675857</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.005093498967585618</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.1930325977</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.1930325977</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$215,A22,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>103.66464270084731</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>103.66464270084731</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>252.07081954699999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.176778197854014</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>150.23744799592774</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>252.07081954699999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>156.0529847638321</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$215,A23,'Species'!$U$2:$U$215))</x:f>
-        <x:v>39336.403762174654</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.176778197854014</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>150.23744799592774</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>37870.476642983296</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>1465.9271191913576</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0387089693380707</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.03870896933807056</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>1.5714985102999999</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>1.5714985102999999</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$215,A24,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>991.5485269134672</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
-        <x:v>991.5485269134672</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>2.317700608</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.97</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>933.2543007969915</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>2.317700608</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$215,A25,'Species'!$U$2:$U$215))</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>2163.004060375802</x:v>
       </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.97</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
-        <x:v>2163.004060375802</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R120bf2a672d74353"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16d4e734d6014cff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17277,7 +15898,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -17376,7 +15997,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>188913523.83892512</x:v>
+        <x:v>146072990.1542673</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17390,7 +16011,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>188913523.8389252</x:v>
+        <x:v>143010668.57291692</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17404,7 +16025,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-42840533.68465787</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17418,7 +16039,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-45902855.26600826</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17429,9 +16050,9 @@
         <x:v>EEZ_694</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -17443,47 +16064,19 @@
         <x:v>EEZ_694</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_694</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_694</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1f98836806549c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38446df514284d34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17530,7 +16123,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
